--- a/frame_output.xlsx
+++ b/frame_output.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1320" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1364" uniqueCount="18">
   <si>
     <t>NodeNo</t>
   </si>
@@ -118,11 +118,11 @@
   <dimension ref="A1:E352"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="7.88671875" customWidth="true"/>
-    <col min="2" max="2" width="11.77734375" customWidth="true"/>
-    <col min="3" max="3" width="12.5546875" customWidth="true"/>
-    <col min="4" max="4" width="5.5546875" customWidth="true"/>
-    <col min="5" max="5" width="5.5546875" customWidth="true"/>
+    <col min="1" max="1" width="8.5703125" customWidth="true"/>
+    <col min="2" max="2" width="12.85546875" customWidth="true"/>
+    <col min="3" max="3" width="12.7109375" customWidth="true"/>
+    <col min="4" max="4" width="5.7109375" customWidth="true"/>
+    <col min="5" max="5" width="5.7109375" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6118,17 +6118,17 @@
   <dimension ref="A1:K153"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="7.44140625" customWidth="true"/>
-    <col min="2" max="2" width="11.33203125" customWidth="true"/>
-    <col min="3" max="3" width="4" customWidth="true"/>
-    <col min="4" max="4" width="4" customWidth="true"/>
-    <col min="5" max="5" width="4" customWidth="true"/>
-    <col min="6" max="6" width="4" customWidth="true"/>
-    <col min="7" max="7" width="4" customWidth="true"/>
-    <col min="8" max="8" width="4" customWidth="true"/>
-    <col min="9" max="9" width="4" customWidth="true"/>
-    <col min="10" max="10" width="4" customWidth="true"/>
-    <col min="11" max="11" width="4.5546875" customWidth="true"/>
+    <col min="1" max="1" width="8.140625" customWidth="true"/>
+    <col min="2" max="2" width="12.42578125" customWidth="true"/>
+    <col min="3" max="3" width="4.140625" customWidth="true"/>
+    <col min="4" max="4" width="4.140625" customWidth="true"/>
+    <col min="5" max="5" width="4.140625" customWidth="true"/>
+    <col min="6" max="6" width="4.140625" customWidth="true"/>
+    <col min="7" max="7" width="4.140625" customWidth="true"/>
+    <col min="8" max="8" width="4.140625" customWidth="true"/>
+    <col min="9" max="9" width="4.140625" customWidth="true"/>
+    <col min="10" max="10" width="4.140625" customWidth="true"/>
+    <col min="11" max="11" width="4.85546875" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11495,12 +11495,12 @@
   <dimension ref="A1:F1217"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="7.44140625" customWidth="true"/>
-    <col min="2" max="2" width="9.77734375" customWidth="true"/>
-    <col min="3" max="3" width="10.6640625" customWidth="true"/>
-    <col min="4" max="4" width="12.5546875" customWidth="true"/>
-    <col min="5" max="5" width="5.5546875" customWidth="true"/>
-    <col min="6" max="6" width="5.5546875" customWidth="true"/>
+    <col min="1" max="1" width="8.140625" customWidth="true"/>
+    <col min="2" max="2" width="10.42578125" customWidth="true"/>
+    <col min="3" max="3" width="11.7109375" customWidth="true"/>
+    <col min="4" max="4" width="12.7109375" customWidth="true"/>
+    <col min="5" max="5" width="5.7109375" customWidth="true"/>
+    <col min="6" max="6" width="5.7109375" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/frame_output.xlsx
+++ b/frame_output.xlsx
@@ -1,7 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fileVersion appName="libxl" rupBuild="4.6.0"/>
   <workbookPr/>
   <bookViews>
     <workbookView activeTab="0"/>
@@ -16,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1364" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="3322" uniqueCount="18">
   <si>
     <t>NodeNo</t>
   </si>

--- a/frame_output.xlsx
+++ b/frame_output.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="3322" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="3366" uniqueCount="18">
   <si>
     <t>NodeNo</t>
   </si>

--- a/frame_output.xlsx
+++ b/frame_output.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="3366" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="3410" uniqueCount="18">
   <si>
     <t>NodeNo</t>
   </si>

--- a/frame_output.xlsx
+++ b/frame_output.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="3410" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="3476" uniqueCount="18">
   <si>
     <t>NodeNo</t>
   </si>

--- a/frame_output.xlsx
+++ b/frame_output.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="3476" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="3630" uniqueCount="18">
   <si>
     <t>NodeNo</t>
   </si>
